--- a/data/seminars.xlsx
+++ b/data/seminars.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346B0409-12AB-4096-91B9-18A3D8C67DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC26D6E9-C115-430F-9E2A-68D51AB1D4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="650" yWindow="11940" windowWidth="37330" windowHeight="8700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
   <si>
     <t>date</t>
   </si>
@@ -301,6 +301,15 @@
   </si>
   <si>
     <t>events/20260519/20260519_EML_EMA_stats.pdf</t>
+  </si>
+  <si>
+    <t>https://psiweb.org/vod/item/causal-inference-sig-webinar--modern-approaches-for-covariate-adjustment-in-clinical-trials</t>
+  </si>
+  <si>
+    <t>Causal Inference SIG Webinar: Modern Approaches for Covariate Adjustment in Clinical Trials</t>
+  </si>
+  <si>
+    <t>Co-organizers</t>
   </si>
 </sst>
 </file>
@@ -640,29 +649,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P21"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="43.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="58" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.1796875" style="1"/>
+    <col min="15" max="15" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -712,7 +721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="str">
         <f>"06.05.2024"</f>
         <v>06.05.2024</v>
@@ -745,7 +754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>"17.06.2024"</f>
         <v>17.06.2024</v>
@@ -781,7 +790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f t="shared" ref="A4:A5" si="0">"17.06.2024"</f>
         <v>17.06.2024</v>
@@ -805,7 +814,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>17.06.2024</v>
@@ -829,7 +838,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>"06.07.2024"</f>
         <v>06.07.2024</v>
@@ -856,7 +865,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f t="shared" ref="A7:A10" si="1">"06.07.2024"</f>
         <v>06.07.2024</v>
@@ -880,7 +889,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f t="shared" si="1"/>
         <v>06.07.2024</v>
@@ -904,7 +913,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f t="shared" si="1"/>
         <v>06.07.2024</v>
@@ -928,7 +937,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f t="shared" si="1"/>
         <v>06.07.2024</v>
@@ -952,7 +961,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <f>"13.11.2024"</f>
         <v>13.11.2024</v>
@@ -970,7 +979,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <f>"13.09.2025"</f>
         <v>13.09.2025</v>
@@ -982,7 +991,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>"13.05.2025"</f>
         <v>13.05.2025</v>
@@ -1015,7 +1024,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f>"10.09.2025"</f>
         <v>10.09.2025</v>
@@ -1054,7 +1063,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
         <f>"10.09.2025"</f>
         <v>10.09.2025</v>
@@ -1078,7 +1087,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <f>"10.09.2025"</f>
         <v>10.09.2025</v>
@@ -1102,7 +1111,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <f>"03.11.2025"</f>
         <v>03.11.2025</v>
@@ -1144,7 +1153,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <f>"15.04.2026"</f>
         <v>15.04.2026</v>
@@ -1165,7 +1174,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f>"12.05.2026"</f>
         <v>12.05.2026</v>
@@ -1186,7 +1195,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f>"19.05.2026"</f>
         <v>19.05.2026</v>
@@ -1202,6 +1211,30 @@
       </c>
       <c r="J20" s="1" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="255" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="str">
+        <f>"30.06.2026"</f>
+        <v>30.06.2026</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
